--- a/results/tables.xlsx
+++ b/results/tables.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbrev\Documents\Acadêmico\Simulações\videogame\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B5611E-EAEA-4869-927A-DBAED1C06804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC42FF3-34FF-4103-9773-17803BF11051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Screenshots" sheetId="2" r:id="rId1"/>
     <sheet name="Results" sheetId="1" r:id="rId2"/>
-    <sheet name="Results Feat-Extr" sheetId="3" r:id="rId3"/>
-    <sheet name="ss-init" sheetId="4" r:id="rId4"/>
-    <sheet name="ss-init (2)" sheetId="5" r:id="rId5"/>
-    <sheet name="DataAug" sheetId="6" r:id="rId6"/>
-    <sheet name="Interpolation" sheetId="7" r:id="rId7"/>
+    <sheet name="Results Merged" sheetId="8" r:id="rId3"/>
+    <sheet name="Results Feat-Extr" sheetId="3" r:id="rId4"/>
+    <sheet name="ss-init" sheetId="4" r:id="rId5"/>
+    <sheet name="ss-init (2)" sheetId="5" r:id="rId6"/>
+    <sheet name="DataAug" sheetId="6" r:id="rId7"/>
+    <sheet name="Interpolation" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="87">
   <si>
     <t>System</t>
   </si>
@@ -306,6 +307,18 @@
   <si>
     <t>lanczos</t>
   </si>
+  <si>
+    <t>ResNet50</t>
+  </si>
+  <si>
+    <t>ResNet152</t>
+  </si>
+  <si>
+    <t>MobileNet</t>
+  </si>
+  <si>
+    <t>EfficientNetB0</t>
+  </si>
 </sst>
 </file>
 
@@ -492,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -901,13 +914,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -916,26 +947,74 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1822,7 +1901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z50"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
@@ -2022,7 +2101,7 @@
         <v>0.54530000000000001</v>
       </c>
       <c r="T3" s="102">
-        <f t="shared" ref="T3:T23" si="2">AVERAGE(Q3:Q3)</f>
+        <f>AVERAGE(Q3:Q3)</f>
         <v>0.51060000000000005</v>
       </c>
       <c r="Z3" s="11">
@@ -2087,7 +2166,7 @@
         <v>0.40579999999999999</v>
       </c>
       <c r="T4" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q4:Q4)</f>
         <v>0.55910000000000004</v>
       </c>
       <c r="Z4" s="11">
@@ -2152,7 +2231,7 @@
         <v>0.73209999999999997</v>
       </c>
       <c r="T5" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q5:Q5)</f>
         <v>0.69740000000000002</v>
       </c>
       <c r="Z5" s="11">
@@ -2217,7 +2296,7 @@
         <v>0.35070000000000001</v>
       </c>
       <c r="T6" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q6:Q6)</f>
         <v>0.52429999999999999</v>
       </c>
       <c r="Z6" s="11">
@@ -2282,7 +2361,7 @@
         <v>0.33660000000000001</v>
       </c>
       <c r="T7" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q7:Q7)</f>
         <v>0.53120000000000001</v>
       </c>
       <c r="Z7" s="11">
@@ -2347,7 +2426,7 @@
         <v>0.50629999999999997</v>
       </c>
       <c r="T8" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q8:Q8)</f>
         <v>0.52070000000000005</v>
       </c>
       <c r="Z8" s="11">
@@ -2412,7 +2491,7 @@
         <v>0.54700000000000004</v>
       </c>
       <c r="T9" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q9:Q9)</f>
         <v>0.4289</v>
       </c>
       <c r="Z9" s="11">
@@ -2477,7 +2556,7 @@
         <v>0.57969999999999999</v>
       </c>
       <c r="T10" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q10:Q10)</f>
         <v>0.57030000000000003</v>
       </c>
       <c r="Z10" s="11">
@@ -2542,7 +2621,7 @@
         <v>0.57399999999999995</v>
       </c>
       <c r="T11" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q11:Q11)</f>
         <v>0.5161</v>
       </c>
       <c r="Z11" s="11">
@@ -2607,7 +2686,7 @@
         <v>0.44600000000000001</v>
       </c>
       <c r="T12" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q12:Q12)</f>
         <v>0.51080000000000003</v>
       </c>
       <c r="Z12" s="11">
@@ -2672,7 +2751,7 @@
         <v>0.22409999999999999</v>
       </c>
       <c r="T13" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q13:Q13)</f>
         <v>0.5776</v>
       </c>
       <c r="Z13" s="11">
@@ -2737,7 +2816,7 @@
         <v>0.55059999999999998</v>
       </c>
       <c r="T14" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q14:Q14)</f>
         <v>0.52769999999999995</v>
       </c>
       <c r="Z14" s="11">
@@ -2802,7 +2881,7 @@
         <v>0.59319999999999995</v>
       </c>
       <c r="T15" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q15:Q15)</f>
         <v>0.42649999999999999</v>
       </c>
       <c r="Z15" s="11">
@@ -2867,7 +2946,7 @@
         <v>0.46529999999999999</v>
       </c>
       <c r="T16" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q16:Q16)</f>
         <v>0.45319999999999999</v>
       </c>
       <c r="Z16" s="11">
@@ -2932,7 +3011,7 @@
         <v>0.43569999999999998</v>
       </c>
       <c r="T17" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q17:Q17)</f>
         <v>0.60660000000000003</v>
       </c>
       <c r="Z17" s="11">
@@ -2997,7 +3076,7 @@
         <v>0.33079999999999998</v>
       </c>
       <c r="T18" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q18:Q18)</f>
         <v>0.50190000000000001</v>
       </c>
       <c r="Z18" s="11">
@@ -3062,7 +3141,7 @@
         <v>0.46779999999999999</v>
       </c>
       <c r="T19" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q19:Q19)</f>
         <v>0.38250000000000001</v>
       </c>
     </row>
@@ -3124,7 +3203,7 @@
         <v>0.3392</v>
       </c>
       <c r="T20" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q20:Q20)</f>
         <v>0.3488</v>
       </c>
     </row>
@@ -3186,7 +3265,7 @@
         <v>0.40229999999999999</v>
       </c>
       <c r="T21" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q21:Q21)</f>
         <v>0.50570000000000004</v>
       </c>
     </row>
@@ -3248,7 +3327,7 @@
         <v>0.58209999999999995</v>
       </c>
       <c r="T22" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q22:Q22)</f>
         <v>0.52500000000000002</v>
       </c>
     </row>
@@ -3310,7 +3389,7 @@
         <v>0.25569999999999998</v>
       </c>
       <c r="T23" s="102">
-        <f t="shared" si="2"/>
+        <f>AVERAGE(Q23:Q23)</f>
         <v>0.31169999999999998</v>
       </c>
     </row>
@@ -3319,43 +3398,43 @@
         <v>22</v>
       </c>
       <c r="C24" s="106">
-        <f t="shared" ref="C24:L24" si="3">AVERAGE(C2:C23)</f>
+        <f t="shared" ref="C24:L24" si="2">AVERAGE(C2:C23)</f>
         <v>0.28838181818181818</v>
       </c>
       <c r="D24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.69495454545454538</v>
       </c>
       <c r="E24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.6685545454545454</v>
       </c>
       <c r="F24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.69791727272727266</v>
       </c>
       <c r="G24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.74456545454545453</v>
       </c>
       <c r="H24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.75770909090909089</v>
       </c>
       <c r="I24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.7111054545454546</v>
       </c>
       <c r="J24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.73433363636363636</v>
       </c>
       <c r="K24" s="106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.7450681818181818</v>
       </c>
       <c r="L24" s="107">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.77444090909090935</v>
       </c>
       <c r="M24" s="108">
@@ -3476,7 +3555,7 @@
         <v>2.7400000000000001E-2</v>
       </c>
       <c r="M28" s="102">
-        <f t="shared" ref="M28:M49" si="4">AVERAGE(C28:K28)</f>
+        <f t="shared" ref="M28:M49" si="3">AVERAGE(C28:K28)</f>
         <v>4.7877777777777783E-2</v>
       </c>
       <c r="N28" s="102"/>
@@ -3532,7 +3611,7 @@
         <v>2.4E-2</v>
       </c>
       <c r="M29" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6311111111111112E-2</v>
       </c>
       <c r="N29" s="102"/>
@@ -3549,7 +3628,7 @@
         <v>1.38E-2</v>
       </c>
       <c r="T29" s="102">
-        <f t="shared" ref="T29:T49" si="5">AVERAGE(Q29:S29)</f>
+        <f>AVERAGE(Q29:S29)</f>
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
@@ -3588,7 +3667,7 @@
         <v>1.1900000000000001E-2</v>
       </c>
       <c r="M30" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.4988888888888889E-2</v>
       </c>
       <c r="N30" s="102"/>
@@ -3605,7 +3684,7 @@
         <v>0.25990000000000002</v>
       </c>
       <c r="T30" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q30:S30)</f>
         <v>0.1345666666666667</v>
       </c>
     </row>
@@ -3644,7 +3723,7 @@
         <v>9.4000000000000004E-3</v>
       </c>
       <c r="M31" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6633333333333332E-2</v>
       </c>
       <c r="N31" s="102"/>
@@ -3661,7 +3740,7 @@
         <v>3.2599999999999997E-2</v>
       </c>
       <c r="T31" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q31:S31)</f>
         <v>5.1766666666666662E-2</v>
       </c>
     </row>
@@ -3700,7 +3779,7 @@
         <v>3.2199999999999999E-2</v>
       </c>
       <c r="M32" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>5.2944444444444447E-2</v>
       </c>
       <c r="N32" s="102"/>
@@ -3717,7 +3796,7 @@
         <v>0.28399999999999997</v>
       </c>
       <c r="T32" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q32:S32)</f>
         <v>0.15590000000000001</v>
       </c>
     </row>
@@ -3756,7 +3835,7 @@
         <v>1.72E-2</v>
       </c>
       <c r="M33" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.0477777777777777E-2</v>
       </c>
       <c r="N33" s="102"/>
@@ -3773,7 +3852,7 @@
         <v>0.32600000000000001</v>
       </c>
       <c r="T33" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q33:S33)</f>
         <v>0.17416666666666666</v>
       </c>
     </row>
@@ -3812,7 +3891,7 @@
         <v>1.11E-2</v>
       </c>
       <c r="M34" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="N34" s="102"/>
@@ -3829,7 +3908,7 @@
         <v>7.1499999999999994E-2</v>
       </c>
       <c r="T34" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q34:S34)</f>
         <v>5.1299999999999991E-2</v>
       </c>
     </row>
@@ -3868,7 +3947,7 @@
         <v>2.4899999999999999E-2</v>
       </c>
       <c r="M35" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.6566666666666666E-2</v>
       </c>
       <c r="N35" s="102"/>
@@ -3885,7 +3964,7 @@
         <v>3.2300000000000002E-2</v>
       </c>
       <c r="T35" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q35:S35)</f>
         <v>7.0566666666666666E-2</v>
       </c>
     </row>
@@ -3924,7 +4003,7 @@
         <v>3.1899999999999998E-2</v>
       </c>
       <c r="M36" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.5511111111111118E-2</v>
       </c>
       <c r="N36" s="102"/>
@@ -3941,7 +4020,7 @@
         <v>0.25750000000000001</v>
       </c>
       <c r="T36" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q36:S36)</f>
         <v>0.15696666666666667</v>
       </c>
     </row>
@@ -3980,7 +4059,7 @@
         <v>1.83E-2</v>
       </c>
       <c r="M37" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.0455555555555553E-2</v>
       </c>
       <c r="N37" s="102"/>
@@ -3997,7 +4076,7 @@
         <v>8.2699999999999996E-2</v>
       </c>
       <c r="T37" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q37:S37)</f>
         <v>4.4899999999999995E-2</v>
       </c>
     </row>
@@ -4036,7 +4115,7 @@
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="M38" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.7188888888888889E-2</v>
       </c>
       <c r="N38" s="102"/>
@@ -4053,7 +4132,7 @@
         <v>0.2213</v>
       </c>
       <c r="T38" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q38:S38)</f>
         <v>0.11133333333333333</v>
       </c>
     </row>
@@ -4092,7 +4171,7 @@
         <v>2.3E-2</v>
       </c>
       <c r="M39" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.4411111111111112E-2</v>
       </c>
       <c r="N39" s="102"/>
@@ -4109,7 +4188,7 @@
         <v>0.2437</v>
       </c>
       <c r="T39" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q39:S39)</f>
         <v>0.16713333333333336</v>
       </c>
     </row>
@@ -4148,7 +4227,7 @@
         <v>1.32E-2</v>
       </c>
       <c r="M40" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>4.1322222222222219E-2</v>
       </c>
       <c r="N40" s="102"/>
@@ -4165,7 +4244,7 @@
         <v>0.26550000000000001</v>
       </c>
       <c r="T40" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q40:S40)</f>
         <v>0.13566666666666669</v>
       </c>
     </row>
@@ -4204,7 +4283,7 @@
         <v>1.17E-2</v>
       </c>
       <c r="M41" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.6844444444444445E-2</v>
       </c>
       <c r="N41" s="102"/>
@@ -4221,7 +4300,7 @@
         <v>2.5899999999999999E-2</v>
       </c>
       <c r="T41" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q41:S41)</f>
         <v>0.13176666666666667</v>
       </c>
     </row>
@@ -4260,7 +4339,7 @@
         <v>3.04E-2</v>
       </c>
       <c r="M42" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.692222222222222E-2</v>
       </c>
       <c r="N42" s="102"/>
@@ -4277,7 +4356,7 @@
         <v>2.6499999999999999E-2</v>
       </c>
       <c r="T42" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q42:S42)</f>
         <v>5.2666666666666667E-2</v>
       </c>
     </row>
@@ -4316,7 +4395,7 @@
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="M43" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.294444444444445E-2</v>
       </c>
       <c r="N43" s="102"/>
@@ -4333,7 +4412,7 @@
         <v>0.32850000000000001</v>
       </c>
       <c r="T43" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q43:S43)</f>
         <v>0.19400000000000003</v>
       </c>
     </row>
@@ -4372,7 +4451,7 @@
         <v>2.4299999999999999E-2</v>
       </c>
       <c r="M44" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3.1033333333333333E-2</v>
       </c>
       <c r="N44" s="102"/>
@@ -4389,7 +4468,7 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="T44" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q44:S44)</f>
         <v>9.6000000000000016E-2</v>
       </c>
     </row>
@@ -4428,7 +4507,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="M45" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6044444444444448E-2</v>
       </c>
       <c r="N45" s="102"/>
@@ -4484,7 +4563,7 @@
         <v>2.1700000000000001E-2</v>
       </c>
       <c r="M46" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.1066666666666664E-2</v>
       </c>
       <c r="N46" s="102"/>
@@ -4501,7 +4580,7 @@
         <v>0.17749999999999999</v>
       </c>
       <c r="T46" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q46:S46)</f>
         <v>0.14126666666666668</v>
       </c>
     </row>
@@ -4540,7 +4619,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
       <c r="M47" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>1.6422222222222223E-2</v>
       </c>
       <c r="N47" s="102"/>
@@ -4557,7 +4636,7 @@
         <v>80</v>
       </c>
       <c r="T47" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q47:S47)</f>
         <v>6.5599999999999992E-2</v>
       </c>
     </row>
@@ -4596,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0.10805555555555556</v>
       </c>
       <c r="N48" s="102"/>
@@ -4613,7 +4692,7 @@
         <v>0.22969999999999999</v>
       </c>
       <c r="T48" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q48:S48)</f>
         <v>0.17760000000000001</v>
       </c>
     </row>
@@ -4652,7 +4731,7 @@
         <v>2.52E-2</v>
       </c>
       <c r="M49" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2.8066666666666667E-2</v>
       </c>
       <c r="N49" s="102"/>
@@ -4669,7 +4748,7 @@
         <v>0.1173</v>
       </c>
       <c r="T49" s="102">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(Q49:S49)</f>
         <v>7.3966666666666667E-2</v>
       </c>
     </row>
@@ -4678,15 +4757,15 @@
         <v>22</v>
       </c>
       <c r="C50" s="106">
-        <f t="shared" ref="C50:L50" si="6">AVERAGE(C28:C49)</f>
+        <f t="shared" ref="C50:L50" si="4">AVERAGE(C28:C49)</f>
         <v>0.11708636363636367</v>
       </c>
       <c r="D50" s="106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.3418181818181817E-2</v>
       </c>
       <c r="E50" s="106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.4604545454545455E-2</v>
       </c>
       <c r="F50" s="106">
@@ -4710,11 +4789,11 @@
         <v>2.4190909090909093E-2</v>
       </c>
       <c r="K50" s="106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.2100000000000002E-2</v>
       </c>
       <c r="L50" s="106">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>2.0154545454545456E-2</v>
       </c>
       <c r="M50" s="108">
@@ -4741,6 +4820,33 @@
         <f>AVERAGE(T28:T49)</f>
         <v>0.10466212121212121</v>
       </c>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4749,6 +4855,2793 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109276F4-5D9B-4945-984A-16FAAE491FC2}">
+  <dimension ref="A1:AK56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.26953125" style="1" customWidth="1"/>
+    <col min="5" max="8" width="11.54296875" style="5" customWidth="1"/>
+    <col min="9" max="10" width="11.453125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12.6328125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="11.1796875" style="1" customWidth="1"/>
+    <col min="15" max="18" width="12.6328125" customWidth="1"/>
+    <col min="19" max="20" width="12.7265625" customWidth="1"/>
+    <col min="21" max="22" width="11.26953125" customWidth="1"/>
+    <col min="23" max="25" width="13.90625" customWidth="1"/>
+    <col min="27" max="27" width="19.1796875" customWidth="1"/>
+    <col min="30" max="30" width="7.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="158" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="152"/>
+      <c r="E1" s="162" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="153"/>
+      <c r="G1" s="162" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="171"/>
+      <c r="I1" s="163" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="155"/>
+      <c r="K1" s="163" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="155"/>
+      <c r="M1" s="163" t="s">
+        <v>75</v>
+      </c>
+      <c r="N1" s="155"/>
+      <c r="O1" s="163" t="s">
+        <v>86</v>
+      </c>
+      <c r="P1" s="155"/>
+      <c r="Q1" s="163" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="155"/>
+      <c r="S1" s="163" t="s">
+        <v>55</v>
+      </c>
+      <c r="T1" s="155"/>
+      <c r="U1" s="163" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="155"/>
+      <c r="W1" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="155"/>
+      <c r="Y1" s="139"/>
+      <c r="AK1" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="159">
+        <v>0.48470000000000002</v>
+      </c>
+      <c r="D2" s="160">
+        <v>0.34870000000000001</v>
+      </c>
+      <c r="E2" s="159">
+        <v>0.89249999999999996</v>
+      </c>
+      <c r="F2" s="160">
+        <v>5.7999999999999996E-3</v>
+      </c>
+      <c r="G2" s="159">
+        <v>0.879</v>
+      </c>
+      <c r="H2" s="136">
+        <v>8.5000000000000006E-3</v>
+      </c>
+      <c r="I2" s="164">
+        <v>0.89246000000000003</v>
+      </c>
+      <c r="J2" s="165">
+        <v>1.1599999999999999E-2</v>
+      </c>
+      <c r="K2" s="164">
+        <v>0.89390000000000003</v>
+      </c>
+      <c r="L2" s="165">
+        <v>1.21E-2</v>
+      </c>
+      <c r="M2" s="159">
+        <v>0.89059999999999995</v>
+      </c>
+      <c r="N2" s="160">
+        <v>5.3E-3</v>
+      </c>
+      <c r="O2" s="164">
+        <v>0.88919999999999999</v>
+      </c>
+      <c r="P2" s="165">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="Q2" s="164">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="R2" s="165">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="S2" s="167">
+        <v>0.90359999999999996</v>
+      </c>
+      <c r="T2" s="160">
+        <v>1.52E-2</v>
+      </c>
+      <c r="U2" s="159">
+        <v>0.88919999999999999</v>
+      </c>
+      <c r="V2" s="160">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="W2" s="159">
+        <f t="shared" ref="W2:X23" si="0">AVERAGE(C2:S2)</f>
+        <v>0.47256823529411773</v>
+      </c>
+      <c r="X2" s="160">
+        <f t="shared" si="0"/>
+        <v>0.44495058823529421</v>
+      </c>
+      <c r="Y2" s="102">
+        <f>_xlfn.STDEV.S(C2:U2)</f>
+        <v>0.42844674973567509</v>
+      </c>
+      <c r="AK2" s="11">
+        <v>0.88170000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="159">
+        <v>0.50870000000000004</v>
+      </c>
+      <c r="D3" s="160">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="E3" s="159">
+        <v>0.65839999999999999</v>
+      </c>
+      <c r="F3" s="160">
+        <v>2.3E-2</v>
+      </c>
+      <c r="G3" s="159">
+        <v>0.65649999999999997</v>
+      </c>
+      <c r="H3" s="136">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="I3" s="164">
+        <v>0.65498000000000001</v>
+      </c>
+      <c r="J3" s="165">
+        <v>3.8699999999999998E-2</v>
+      </c>
+      <c r="K3" s="164">
+        <v>0.67190000000000005</v>
+      </c>
+      <c r="L3" s="165">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="M3" s="159">
+        <v>0.70040000000000002</v>
+      </c>
+      <c r="N3" s="160">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="O3" s="164">
+        <v>0.68452000000000002</v>
+      </c>
+      <c r="P3" s="165">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="Q3" s="164">
+        <v>0.68755999999999995</v>
+      </c>
+      <c r="R3" s="165">
+        <v>3.27E-2</v>
+      </c>
+      <c r="S3" s="159">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="T3" s="160">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="U3" s="167">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="V3" s="160">
+        <v>2.4E-2</v>
+      </c>
+      <c r="W3" s="159">
+        <f t="shared" si="0"/>
+        <v>0.35859176470588239</v>
+      </c>
+      <c r="X3" s="160">
+        <f t="shared" si="0"/>
+        <v>0.3311211764705882</v>
+      </c>
+      <c r="Y3" s="102">
+        <f t="shared" ref="Y3:Y23" si="1">_xlfn.STDEV.S(C3:U3)</f>
+        <v>0.32909155600519147</v>
+      </c>
+      <c r="AK3" s="11">
+        <v>0.70679999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="159">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="D4" s="160">
+        <v>0.21460000000000001</v>
+      </c>
+      <c r="E4" s="159">
+        <v>0.71850000000000003</v>
+      </c>
+      <c r="F4" s="160">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="G4" s="159">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="H4" s="136">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="I4" s="164">
+        <v>0.70698000000000005</v>
+      </c>
+      <c r="J4" s="165">
+        <v>7.7000000000000002E-3</v>
+      </c>
+      <c r="K4" s="164">
+        <v>0.74516000000000004</v>
+      </c>
+      <c r="L4" s="165">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="M4" s="159">
+        <v>0.73740000000000006</v>
+      </c>
+      <c r="N4" s="160">
+        <v>1.14E-2</v>
+      </c>
+      <c r="O4" s="164">
+        <v>0.71242000000000005</v>
+      </c>
+      <c r="P4" s="165">
+        <v>0.01</v>
+      </c>
+      <c r="Q4" s="164">
+        <v>0.74180000000000001</v>
+      </c>
+      <c r="R4" s="165">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="S4" s="159">
+        <v>0.7429</v>
+      </c>
+      <c r="T4" s="160">
+        <v>1.23E-2</v>
+      </c>
+      <c r="U4" s="167">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="V4" s="160">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="W4" s="159">
+        <f t="shared" si="0"/>
+        <v>0.37002117647058819</v>
+      </c>
+      <c r="X4" s="160">
+        <f t="shared" si="0"/>
+        <v>0.35812117647058822</v>
+      </c>
+      <c r="Y4" s="102">
+        <f t="shared" si="1"/>
+        <v>0.35114768381402345</v>
+      </c>
+      <c r="AK4" s="11">
+        <v>0.72889999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="159">
+        <v>0.30549999999999999</v>
+      </c>
+      <c r="D5" s="160">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="E5" s="159">
+        <v>0.77380000000000004</v>
+      </c>
+      <c r="F5" s="160">
+        <v>1.26E-2</v>
+      </c>
+      <c r="G5" s="159">
+        <v>0.75360000000000005</v>
+      </c>
+      <c r="H5" s="136">
+        <v>1.29E-2</v>
+      </c>
+      <c r="I5" s="164">
+        <v>0.75429999999999997</v>
+      </c>
+      <c r="J5" s="165">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="K5" s="164">
+        <v>0.79893999999999998</v>
+      </c>
+      <c r="L5" s="165">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="M5" s="159">
+        <v>0.80189999999999995</v>
+      </c>
+      <c r="N5" s="160">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O5" s="164">
+        <v>0.77712000000000003</v>
+      </c>
+      <c r="P5" s="165">
+        <v>5.4000000000000003E-3</v>
+      </c>
+      <c r="Q5" s="164">
+        <v>0.78342000000000001</v>
+      </c>
+      <c r="R5" s="165">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="S5" s="159">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="T5" s="160">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="U5" s="167">
+        <v>0.80520000000000003</v>
+      </c>
+      <c r="V5" s="160">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="W5" s="159">
+        <f t="shared" si="0"/>
+        <v>0.39816941176470583</v>
+      </c>
+      <c r="X5" s="160">
+        <f t="shared" si="0"/>
+        <v>0.38069294117647051</v>
+      </c>
+      <c r="Y5" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38002396701580909</v>
+      </c>
+      <c r="AK5" s="11">
+        <v>0.78210000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="159">
+        <v>0.28810000000000002</v>
+      </c>
+      <c r="D6" s="160">
+        <v>0.2331</v>
+      </c>
+      <c r="E6" s="159">
+        <v>0.68430000000000002</v>
+      </c>
+      <c r="F6" s="160">
+        <v>2.9399999999999999E-2</v>
+      </c>
+      <c r="G6" s="159">
+        <v>0.68079999999999996</v>
+      </c>
+      <c r="H6" s="136">
+        <v>0.02</v>
+      </c>
+      <c r="I6" s="164">
+        <v>0.67513999999999996</v>
+      </c>
+      <c r="J6" s="165">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="K6" s="164">
+        <v>0.73065999999999998</v>
+      </c>
+      <c r="L6" s="165">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="M6" s="159">
+        <v>0.73440000000000005</v>
+      </c>
+      <c r="N6" s="160">
+        <v>2.53E-2</v>
+      </c>
+      <c r="O6" s="164">
+        <v>0.73262000000000005</v>
+      </c>
+      <c r="P6" s="165">
+        <v>4.3E-3</v>
+      </c>
+      <c r="Q6" s="164">
+        <v>0.72463999999999995</v>
+      </c>
+      <c r="R6" s="165">
+        <v>3.95E-2</v>
+      </c>
+      <c r="S6" s="159">
+        <v>0.73070000000000002</v>
+      </c>
+      <c r="T6" s="160">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="U6" s="167">
+        <v>0.74560000000000004</v>
+      </c>
+      <c r="V6" s="160">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="W6" s="159">
+        <f t="shared" si="0"/>
+        <v>0.37739176470588232</v>
+      </c>
+      <c r="X6" s="160">
+        <f t="shared" si="0"/>
+        <v>0.36292705882352944</v>
+      </c>
+      <c r="Y6" s="102">
+        <f t="shared" si="1"/>
+        <v>0.33565513143823494</v>
+      </c>
+      <c r="AK6" s="11">
+        <v>0.72170000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="159">
+        <v>0.4824</v>
+      </c>
+      <c r="D7" s="160">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="E7" s="159">
+        <v>0.68230000000000002</v>
+      </c>
+      <c r="F7" s="160">
+        <v>2.92E-2</v>
+      </c>
+      <c r="G7" s="159">
+        <v>0.68420000000000003</v>
+      </c>
+      <c r="H7" s="136">
+        <v>1.29E-2</v>
+      </c>
+      <c r="I7" s="164">
+        <v>0.67235999999999996</v>
+      </c>
+      <c r="J7" s="165">
+        <v>4.9200000000000001E-2</v>
+      </c>
+      <c r="K7" s="164">
+        <v>0.72470000000000001</v>
+      </c>
+      <c r="L7" s="165">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="M7" s="167">
+        <v>0.74509999999999998</v>
+      </c>
+      <c r="N7" s="160">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="O7" s="164">
+        <v>0.70152000000000003</v>
+      </c>
+      <c r="P7" s="165">
+        <v>0.03</v>
+      </c>
+      <c r="Q7" s="164">
+        <v>0.71423999999999999</v>
+      </c>
+      <c r="R7" s="165">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="S7" s="159">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="T7" s="160">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="U7" s="159">
+        <v>0.72889999999999999</v>
+      </c>
+      <c r="V7" s="160">
+        <v>1.72E-2</v>
+      </c>
+      <c r="W7" s="159">
+        <f t="shared" si="0"/>
+        <v>0.37225411764705885</v>
+      </c>
+      <c r="X7" s="160">
+        <f t="shared" si="0"/>
+        <v>0.34746000000000005</v>
+      </c>
+      <c r="Y7" s="102">
+        <f t="shared" si="1"/>
+        <v>0.33974762580445794</v>
+      </c>
+      <c r="AK7" s="11">
+        <v>0.73429999999999995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="159">
+        <v>0.20780000000000001</v>
+      </c>
+      <c r="D8" s="160">
+        <v>0.13980000000000001</v>
+      </c>
+      <c r="E8" s="159">
+        <v>0.70040000000000002</v>
+      </c>
+      <c r="F8" s="160">
+        <v>1.09E-2</v>
+      </c>
+      <c r="G8" s="159">
+        <v>0.67190000000000005</v>
+      </c>
+      <c r="H8" s="136">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I8" s="164">
+        <v>0.69725999999999999</v>
+      </c>
+      <c r="J8" s="165">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="K8" s="164">
+        <v>0.74939999999999996</v>
+      </c>
+      <c r="L8" s="165">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="M8" s="159">
+        <v>0.751</v>
+      </c>
+      <c r="N8" s="160">
+        <v>1.35E-2</v>
+      </c>
+      <c r="O8" s="164">
+        <v>0.67279999999999995</v>
+      </c>
+      <c r="P8" s="165">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="Q8" s="164">
+        <v>0.68413999999999997</v>
+      </c>
+      <c r="R8" s="165">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="S8" s="159">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="T8" s="160">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="U8" s="167">
+        <v>0.7591</v>
+      </c>
+      <c r="V8" s="160">
+        <v>1.11E-2</v>
+      </c>
+      <c r="W8" s="159">
+        <f t="shared" si="0"/>
+        <v>0.35802352941176474</v>
+      </c>
+      <c r="X8" s="160">
+        <f t="shared" si="0"/>
+        <v>0.34637647058823534</v>
+      </c>
+      <c r="Y8" s="102">
+        <f t="shared" si="1"/>
+        <v>0.3447091234870418</v>
+      </c>
+      <c r="AK8" s="11">
+        <v>0.67889999999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="159">
+        <v>0.27089999999999997</v>
+      </c>
+      <c r="D9" s="160">
+        <v>0.2175</v>
+      </c>
+      <c r="E9" s="159">
+        <v>0.67410000000000003</v>
+      </c>
+      <c r="F9" s="160">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="G9" s="159">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="H9" s="136">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="I9" s="164">
+        <v>0.69084000000000001</v>
+      </c>
+      <c r="J9" s="165">
+        <v>1.2E-2</v>
+      </c>
+      <c r="K9" s="164">
+        <v>0.70786000000000004</v>
+      </c>
+      <c r="L9" s="165">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="M9" s="159">
+        <v>0.71189999999999998</v>
+      </c>
+      <c r="N9" s="160">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="O9" s="164">
+        <v>0.67676000000000003</v>
+      </c>
+      <c r="P9" s="165">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="Q9" s="164">
+        <v>0.72265999999999997</v>
+      </c>
+      <c r="R9" s="165">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="S9" s="159">
+        <v>0.74019999999999997</v>
+      </c>
+      <c r="T9" s="160">
+        <v>1.03E-2</v>
+      </c>
+      <c r="U9" s="167">
+        <v>0.74770000000000003</v>
+      </c>
+      <c r="V9" s="160">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="W9" s="159">
+        <f t="shared" si="0"/>
+        <v>0.36853058823529411</v>
+      </c>
+      <c r="X9" s="160">
+        <f t="shared" si="0"/>
+        <v>0.35320117647058824</v>
+      </c>
+      <c r="Y9" s="102">
+        <f t="shared" si="1"/>
+        <v>0.33286264302331647</v>
+      </c>
+      <c r="AK9" s="11">
+        <v>0.72109999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="159">
+        <v>0.23880000000000001</v>
+      </c>
+      <c r="D10" s="160">
+        <v>0.19259999999999999</v>
+      </c>
+      <c r="E10" s="159">
+        <v>0.78459999999999996</v>
+      </c>
+      <c r="F10" s="160">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="G10" s="159">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="H10" s="136">
+        <v>1.15E-2</v>
+      </c>
+      <c r="I10" s="164">
+        <v>0.76537999999999995</v>
+      </c>
+      <c r="J10" s="165">
+        <v>2.06E-2</v>
+      </c>
+      <c r="K10" s="164">
+        <v>0.83265999999999996</v>
+      </c>
+      <c r="L10" s="165">
+        <v>2.07E-2</v>
+      </c>
+      <c r="M10" s="167">
+        <v>0.8367</v>
+      </c>
+      <c r="N10" s="160">
+        <v>1.17E-2</v>
+      </c>
+      <c r="O10" s="164">
+        <v>0.73834</v>
+      </c>
+      <c r="P10" s="165">
+        <v>1.14E-2</v>
+      </c>
+      <c r="Q10" s="164">
+        <v>0.7681</v>
+      </c>
+      <c r="R10" s="165">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="S10" s="159">
+        <v>0.77759999999999996</v>
+      </c>
+      <c r="T10" s="160">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="U10" s="159">
+        <v>0.82279999999999998</v>
+      </c>
+      <c r="V10" s="160">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="W10" s="159">
+        <f t="shared" si="0"/>
+        <v>0.40081058823529409</v>
+      </c>
+      <c r="X10" s="160">
+        <f t="shared" si="0"/>
+        <v>0.38729294117647062</v>
+      </c>
+      <c r="Y10" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38082694025114949</v>
+      </c>
+      <c r="AK10" s="11">
+        <v>0.76470000000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="159">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="D11" s="160">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="E11" s="159">
+        <v>0.70469999999999999</v>
+      </c>
+      <c r="F11" s="160">
+        <v>1.61E-2</v>
+      </c>
+      <c r="G11" s="159">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="H11" s="136">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="I11" s="164">
+        <v>0.65210000000000001</v>
+      </c>
+      <c r="J11" s="165">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="K11" s="164">
+        <v>0.75129999999999997</v>
+      </c>
+      <c r="L11" s="165">
+        <v>1.26E-2</v>
+      </c>
+      <c r="M11" s="167">
+        <v>0.75360000000000005</v>
+      </c>
+      <c r="N11" s="160">
+        <v>1.9E-2</v>
+      </c>
+      <c r="O11" s="164">
+        <v>0.63488</v>
+      </c>
+      <c r="P11" s="165">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="Q11" s="164">
+        <v>0.67349999999999999</v>
+      </c>
+      <c r="R11" s="165">
+        <v>0.03</v>
+      </c>
+      <c r="S11" s="159">
+        <v>0.67579999999999996</v>
+      </c>
+      <c r="T11" s="160">
+        <v>9.7000000000000003E-3</v>
+      </c>
+      <c r="U11" s="159">
+        <v>0.74990000000000001</v>
+      </c>
+      <c r="V11" s="160">
+        <v>1.83E-2</v>
+      </c>
+      <c r="W11" s="159">
+        <f t="shared" si="0"/>
+        <v>0.33741647058823532</v>
+      </c>
+      <c r="X11" s="160">
+        <f t="shared" si="0"/>
+        <v>0.33530470588235289</v>
+      </c>
+      <c r="Y11" s="102">
+        <f t="shared" si="1"/>
+        <v>0.34680806660455327</v>
+      </c>
+      <c r="AK11" s="11">
+        <v>0.64319999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="159">
+        <v>0.28170000000000001</v>
+      </c>
+      <c r="D12" s="160">
+        <v>0.2271</v>
+      </c>
+      <c r="E12" s="159">
+        <v>0.68869999999999998</v>
+      </c>
+      <c r="F12" s="160">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="G12" s="159">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="H12" s="136">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I12" s="164">
+        <v>0.69394</v>
+      </c>
+      <c r="J12" s="165">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="K12" s="164">
+        <v>0.72728000000000004</v>
+      </c>
+      <c r="L12" s="165">
+        <v>1.4E-2</v>
+      </c>
+      <c r="M12" s="159">
+        <v>0.74109999999999998</v>
+      </c>
+      <c r="N12" s="160">
+        <v>3.8999999999999998E-3</v>
+      </c>
+      <c r="O12" s="164">
+        <v>0.68362000000000001</v>
+      </c>
+      <c r="P12" s="165">
+        <v>1.1299999999999999E-2</v>
+      </c>
+      <c r="Q12" s="164">
+        <v>0.71257999999999999</v>
+      </c>
+      <c r="R12" s="165">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="S12" s="159">
+        <v>0.73450000000000004</v>
+      </c>
+      <c r="T12" s="160">
+        <v>2.52E-2</v>
+      </c>
+      <c r="U12" s="167">
+        <v>0.75139999999999996</v>
+      </c>
+      <c r="V12" s="160">
+        <v>3.2899999999999999E-2</v>
+      </c>
+      <c r="W12" s="159">
+        <f t="shared" si="0"/>
+        <v>0.36678941176470592</v>
+      </c>
+      <c r="X12" s="160">
+        <f t="shared" si="0"/>
+        <v>0.35170117647058818</v>
+      </c>
+      <c r="Y12" s="102">
+        <f t="shared" si="1"/>
+        <v>0.34132881572873924</v>
+      </c>
+      <c r="AK12" s="11">
+        <v>0.70640000000000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="159">
+        <v>5.5500000000000001E-2</v>
+      </c>
+      <c r="D13" s="160">
+        <v>2.92E-2</v>
+      </c>
+      <c r="E13" s="159">
+        <v>0.77490000000000003</v>
+      </c>
+      <c r="F13" s="160">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="G13" s="159">
+        <v>0.75370000000000004</v>
+      </c>
+      <c r="H13" s="136">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I13" s="164">
+        <v>0.74156</v>
+      </c>
+      <c r="J13" s="165">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="K13" s="164">
+        <v>0.82325999999999999</v>
+      </c>
+      <c r="L13" s="165">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="M13" s="167">
+        <v>0.82879999999999998</v>
+      </c>
+      <c r="N13" s="160">
+        <v>1.14E-2</v>
+      </c>
+      <c r="O13" s="164">
+        <v>0.72070000000000001</v>
+      </c>
+      <c r="P13" s="165">
+        <v>8.6E-3</v>
+      </c>
+      <c r="Q13" s="164">
+        <v>0.754</v>
+      </c>
+      <c r="R13" s="165">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="S13" s="159">
+        <v>0.74980000000000002</v>
+      </c>
+      <c r="T13" s="160">
+        <v>1.4E-2</v>
+      </c>
+      <c r="U13" s="159">
+        <v>0.81479999999999997</v>
+      </c>
+      <c r="V13" s="160">
+        <v>2.3E-2</v>
+      </c>
+      <c r="W13" s="159">
+        <f t="shared" si="0"/>
+        <v>0.37164235294117653</v>
+      </c>
+      <c r="X13" s="160">
+        <f t="shared" si="0"/>
+        <v>0.36920117647058825</v>
+      </c>
+      <c r="Y13" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38834762933703598</v>
+      </c>
+      <c r="AK13" s="11">
+        <v>0.75239999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="159">
+        <v>0.45090000000000002</v>
+      </c>
+      <c r="D14" s="160">
+        <v>0.1918</v>
+      </c>
+      <c r="E14" s="159">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="F14" s="160">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="G14" s="159">
+        <v>0.78359999999999996</v>
+      </c>
+      <c r="H14" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="I14" s="164">
+        <v>0.78036000000000005</v>
+      </c>
+      <c r="J14" s="165">
+        <v>6.2E-2</v>
+      </c>
+      <c r="K14" s="164">
+        <v>0.84392</v>
+      </c>
+      <c r="L14" s="165">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="M14" s="159">
+        <v>0.84030000000000005</v>
+      </c>
+      <c r="N14" s="160">
+        <v>1.38E-2</v>
+      </c>
+      <c r="O14" s="164">
+        <v>0.73858000000000001</v>
+      </c>
+      <c r="P14" s="165">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="Q14" s="164">
+        <v>0.79288000000000003</v>
+      </c>
+      <c r="R14" s="165">
+        <v>1.17E-2</v>
+      </c>
+      <c r="S14" s="159">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="T14" s="160">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="U14" s="167">
+        <v>0.84450000000000003</v>
+      </c>
+      <c r="V14" s="160">
+        <v>1.32E-2</v>
+      </c>
+      <c r="W14" s="159">
+        <f t="shared" si="0"/>
+        <v>0.42136117647058824</v>
+      </c>
+      <c r="X14" s="160">
+        <f t="shared" si="0"/>
+        <v>0.39620823529411769</v>
+      </c>
+      <c r="Y14" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38259918060397152</v>
+      </c>
+      <c r="AK14" s="11">
+        <v>0.77049999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>69</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="159">
+        <v>0.38719999999999999</v>
+      </c>
+      <c r="D15" s="160">
+        <v>0.1706</v>
+      </c>
+      <c r="E15" s="159">
+        <v>0.74719999999999998</v>
+      </c>
+      <c r="F15" s="160">
+        <v>1.01E-2</v>
+      </c>
+      <c r="G15" s="159">
+        <v>0.72760000000000002</v>
+      </c>
+      <c r="H15" s="136">
+        <v>1.15E-2</v>
+      </c>
+      <c r="I15" s="164">
+        <v>0.74128000000000005</v>
+      </c>
+      <c r="J15" s="165">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="K15" s="164">
+        <v>0.78586</v>
+      </c>
+      <c r="L15" s="165">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="M15" s="159">
+        <v>0.79430000000000001</v>
+      </c>
+      <c r="N15" s="160">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="O15" s="164">
+        <v>0.7339</v>
+      </c>
+      <c r="P15" s="165">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="Q15" s="164">
+        <v>0.76232</v>
+      </c>
+      <c r="R15" s="165">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="S15" s="159">
+        <v>0.77680000000000005</v>
+      </c>
+      <c r="T15" s="160">
+        <v>8.6E-3</v>
+      </c>
+      <c r="U15" s="167">
+        <v>0.80249999999999999</v>
+      </c>
+      <c r="V15" s="160">
+        <v>1.17E-2</v>
+      </c>
+      <c r="W15" s="159">
+        <f t="shared" si="0"/>
+        <v>0.39349764705882351</v>
+      </c>
+      <c r="X15" s="160">
+        <f t="shared" si="0"/>
+        <v>0.37122705882352941</v>
+      </c>
+      <c r="Y15" s="102">
+        <f t="shared" si="1"/>
+        <v>0.37056088814736154</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>0.75880000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>81</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="159">
+        <v>0.438</v>
+      </c>
+      <c r="D16" s="160">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="E16" s="159">
+        <v>0.6371</v>
+      </c>
+      <c r="F16" s="160">
+        <v>1.32E-2</v>
+      </c>
+      <c r="G16" s="159">
+        <v>0.62909999999999999</v>
+      </c>
+      <c r="H16" s="136">
+        <v>1.6E-2</v>
+      </c>
+      <c r="I16" s="164">
+        <v>0.62180000000000002</v>
+      </c>
+      <c r="J16" s="165">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K16" s="164">
+        <v>0.70731999999999995</v>
+      </c>
+      <c r="L16" s="165">
+        <v>1.47E-2</v>
+      </c>
+      <c r="M16" s="159">
+        <v>0.70930000000000004</v>
+      </c>
+      <c r="N16" s="160">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="O16" s="164">
+        <v>0.66583999999999999</v>
+      </c>
+      <c r="P16" s="165">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="Q16" s="164">
+        <v>0.68901999999999997</v>
+      </c>
+      <c r="R16" s="165">
+        <v>1.12E-2</v>
+      </c>
+      <c r="S16" s="159">
+        <v>0.71819999999999995</v>
+      </c>
+      <c r="T16" s="160">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="U16" s="167">
+        <v>0.7198</v>
+      </c>
+      <c r="V16" s="160">
+        <v>3.04E-2</v>
+      </c>
+      <c r="W16" s="159">
+        <f t="shared" si="0"/>
+        <v>0.35051647058823526</v>
+      </c>
+      <c r="X16" s="160">
+        <f t="shared" si="0"/>
+        <v>0.32529294117647062</v>
+      </c>
+      <c r="Y16" s="102">
+        <f t="shared" si="1"/>
+        <v>0.33214103980861243</v>
+      </c>
+      <c r="AK16" s="11">
+        <v>0.70689999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>82</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="159">
+        <v>0.2006</v>
+      </c>
+      <c r="D17" s="160">
+        <v>0.1762</v>
+      </c>
+      <c r="E17" s="159">
+        <v>0.76349999999999996</v>
+      </c>
+      <c r="F17" s="160">
+        <v>1.54E-2</v>
+      </c>
+      <c r="G17" s="159">
+        <v>0.75819999999999999</v>
+      </c>
+      <c r="H17" s="136">
+        <v>1.49E-2</v>
+      </c>
+      <c r="I17" s="164">
+        <v>0.76380000000000003</v>
+      </c>
+      <c r="J17" s="165">
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="K17" s="164">
+        <v>0.83365999999999996</v>
+      </c>
+      <c r="L17" s="165">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="M17" s="159">
+        <v>0.83050000000000002</v>
+      </c>
+      <c r="N17" s="160">
+        <v>7.9000000000000008E-3</v>
+      </c>
+      <c r="O17" s="164">
+        <v>0.75546000000000002</v>
+      </c>
+      <c r="P17" s="165">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="Q17" s="164">
+        <v>0.76737999999999995</v>
+      </c>
+      <c r="R17" s="165">
+        <v>1.9E-2</v>
+      </c>
+      <c r="S17" s="159">
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="T17" s="160">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="U17" s="167">
+        <v>0.83960000000000001</v>
+      </c>
+      <c r="V17" s="160">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="W17" s="159">
+        <f t="shared" si="0"/>
+        <v>0.39630588235294117</v>
+      </c>
+      <c r="X17" s="160">
+        <f t="shared" si="0"/>
+        <v>0.38547058823529412</v>
+      </c>
+      <c r="Y17" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38326161705345962</v>
+      </c>
+      <c r="AK17" s="11">
+        <v>0.76780000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>132</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="159">
+        <v>0.14710000000000001</v>
+      </c>
+      <c r="D18" s="160">
+        <v>1.44E-2</v>
+      </c>
+      <c r="E18" s="159">
+        <v>0.67689999999999995</v>
+      </c>
+      <c r="F18" s="160">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="G18" s="159">
+        <v>0.66059999999999997</v>
+      </c>
+      <c r="H18" s="136">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I18" s="164">
+        <v>0.65937999999999997</v>
+      </c>
+      <c r="J18" s="165">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="K18" s="164">
+        <v>0.72643999999999997</v>
+      </c>
+      <c r="L18" s="165">
+        <v>4.7300000000000002E-2</v>
+      </c>
+      <c r="M18" s="159">
+        <v>0.73029999999999995</v>
+      </c>
+      <c r="N18" s="160">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="O18" s="164">
+        <v>0.69420000000000004</v>
+      </c>
+      <c r="P18" s="165">
+        <v>1.66E-2</v>
+      </c>
+      <c r="Q18" s="164">
+        <v>0.70064000000000004</v>
+      </c>
+      <c r="R18" s="165">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="S18" s="159">
+        <v>0.71870000000000001</v>
+      </c>
+      <c r="T18" s="160">
+        <v>2.93E-2</v>
+      </c>
+      <c r="U18" s="167">
+        <v>0.74970000000000003</v>
+      </c>
+      <c r="V18" s="160">
+        <v>2.4299999999999999E-2</v>
+      </c>
+      <c r="W18" s="159">
+        <f t="shared" si="0"/>
+        <v>0.35083882352941181</v>
+      </c>
+      <c r="X18" s="160">
+        <f t="shared" si="0"/>
+        <v>0.34390941176470596</v>
+      </c>
+      <c r="Y18" s="102">
+        <f t="shared" si="1"/>
+        <v>0.33996793707092038</v>
+      </c>
+      <c r="AK18" s="11">
+        <v>0.69420000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>141</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="159">
+        <v>0.36909999999999998</v>
+      </c>
+      <c r="D19" s="160">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="E19" s="159">
+        <v>0.52170000000000005</v>
+      </c>
+      <c r="F19" s="160">
+        <v>5.04E-2</v>
+      </c>
+      <c r="G19" s="159">
+        <v>0.54379999999999995</v>
+      </c>
+      <c r="H19" s="136">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="I19" s="164">
+        <v>0.56013999999999997</v>
+      </c>
+      <c r="J19" s="165">
+        <v>6.3E-3</v>
+      </c>
+      <c r="K19" s="164">
+        <v>0.61514000000000002</v>
+      </c>
+      <c r="L19" s="165">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="M19" s="159">
+        <v>0.62190000000000001</v>
+      </c>
+      <c r="N19" s="160">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="O19" s="164">
+        <v>0.59750000000000003</v>
+      </c>
+      <c r="P19" s="165">
+        <v>1.77E-2</v>
+      </c>
+      <c r="Q19" s="164">
+        <v>0.62734000000000001</v>
+      </c>
+      <c r="R19" s="165">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="S19" s="167">
+        <v>0.64770000000000005</v>
+      </c>
+      <c r="T19" s="160">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="U19" s="159">
+        <v>0.63170000000000004</v>
+      </c>
+      <c r="V19" s="160">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="W19" s="159">
+        <f t="shared" si="0"/>
+        <v>0.30784823529411776</v>
+      </c>
+      <c r="X19" s="160">
+        <f t="shared" si="0"/>
+        <v>0.28703647058823534</v>
+      </c>
+      <c r="Y19" s="102">
+        <f t="shared" si="1"/>
+        <v>0.29212725960359931</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>142</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="159">
+        <v>0.25990000000000002</v>
+      </c>
+      <c r="D20" s="160">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="E20" s="159">
+        <v>0.61370000000000002</v>
+      </c>
+      <c r="F20" s="160">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G20" s="159">
+        <v>0.58620000000000005</v>
+      </c>
+      <c r="H20" s="136">
+        <v>1.03E-2</v>
+      </c>
+      <c r="I20" s="164">
+        <v>0.55822000000000005</v>
+      </c>
+      <c r="J20" s="165">
+        <v>1.84E-2</v>
+      </c>
+      <c r="K20" s="164">
+        <v>0.64581999999999995</v>
+      </c>
+      <c r="L20" s="165">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="M20" s="159">
+        <v>0.64959999999999996</v>
+      </c>
+      <c r="N20" s="160">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="O20" s="164">
+        <v>0.57908000000000004</v>
+      </c>
+      <c r="P20" s="165">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="Q20" s="164">
+        <v>0.58575999999999995</v>
+      </c>
+      <c r="R20" s="165">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="S20" s="159">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="T20" s="160">
+        <v>2.92E-2</v>
+      </c>
+      <c r="U20" s="167">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="V20" s="160">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="W20" s="159">
+        <f t="shared" si="0"/>
+        <v>0.31021647058823526</v>
+      </c>
+      <c r="X20" s="160">
+        <f t="shared" si="0"/>
+        <v>0.2966458823529412</v>
+      </c>
+      <c r="Y20" s="102">
+        <f t="shared" si="1"/>
+        <v>0.29731913779345859</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>203</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="159">
+        <v>0.1757</v>
+      </c>
+      <c r="D21" s="160">
+        <v>2.9499999999999998E-2</v>
+      </c>
+      <c r="E21" s="159">
+        <v>0.75629999999999997</v>
+      </c>
+      <c r="F21" s="160">
+        <v>2.3E-2</v>
+      </c>
+      <c r="G21" s="159">
+        <v>0.70279999999999998</v>
+      </c>
+      <c r="H21" s="136">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="I21" s="164">
+        <v>0.73617999999999995</v>
+      </c>
+      <c r="J21" s="165">
+        <v>1.09E-2</v>
+      </c>
+      <c r="K21" s="164">
+        <v>0.80012000000000005</v>
+      </c>
+      <c r="L21" s="165">
+        <v>1.7600000000000001E-2</v>
+      </c>
+      <c r="M21" s="159">
+        <v>0.79900000000000004</v>
+      </c>
+      <c r="N21" s="160">
+        <v>1.55E-2</v>
+      </c>
+      <c r="O21" s="164">
+        <v>0.75114000000000003</v>
+      </c>
+      <c r="P21" s="165">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="Q21" s="164">
+        <v>0.78112000000000004</v>
+      </c>
+      <c r="R21" s="165">
+        <v>1.34E-2</v>
+      </c>
+      <c r="S21" s="168">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="T21" s="166">
+        <v>1.34E-2</v>
+      </c>
+      <c r="U21" s="167">
+        <v>0.80469999999999997</v>
+      </c>
+      <c r="V21" s="160">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="W21" s="159">
+        <f t="shared" si="0"/>
+        <v>0.37796235294117653</v>
+      </c>
+      <c r="X21" s="160">
+        <f t="shared" si="0"/>
+        <v>0.36841529411764706</v>
+      </c>
+      <c r="Y21" s="102">
+        <f t="shared" si="1"/>
+        <v>0.38023974190807019</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>289</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="159">
+        <v>0.3821</v>
+      </c>
+      <c r="D22" s="160">
+        <v>6.93E-2</v>
+      </c>
+      <c r="E22" s="159">
+        <v>0.43930000000000002</v>
+      </c>
+      <c r="F22" s="160">
+        <v>0.1225</v>
+      </c>
+      <c r="G22" s="159">
+        <v>0.27139999999999997</v>
+      </c>
+      <c r="H22" s="136">
+        <v>0.1575</v>
+      </c>
+      <c r="I22" s="164">
+        <v>0.76427999999999996</v>
+      </c>
+      <c r="J22" s="166">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="K22" s="164">
+        <v>0.60711999999999999</v>
+      </c>
+      <c r="L22" s="166">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="M22" s="159">
+        <v>0.78569999999999995</v>
+      </c>
+      <c r="N22" s="160">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="O22" s="164">
+        <v>0.91783999999999999</v>
+      </c>
+      <c r="P22" s="165">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="Q22" s="164">
+        <v>0.97141999999999995</v>
+      </c>
+      <c r="R22" s="165">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="S22" s="168">
+        <v>0.97140000000000004</v>
+      </c>
+      <c r="T22" s="166">
+        <v>5.7099999999999998E-2</v>
+      </c>
+      <c r="U22" s="167">
+        <v>1</v>
+      </c>
+      <c r="V22" s="160">
+        <v>0</v>
+      </c>
+      <c r="W22" s="159">
+        <f t="shared" si="0"/>
+        <v>0.41329176470588236</v>
+      </c>
+      <c r="X22" s="160">
+        <f t="shared" si="0"/>
+        <v>0.39417411764705884</v>
+      </c>
+      <c r="Y22" s="102">
+        <f t="shared" si="1"/>
+        <v>0.36568826399780868</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>288</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="159">
+        <v>0.14949999999999999</v>
+      </c>
+      <c r="D23" s="160">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="E23" s="159">
+        <v>0.59809999999999997</v>
+      </c>
+      <c r="F23" s="160">
+        <v>1.06E-2</v>
+      </c>
+      <c r="G23" s="159">
+        <v>0.54249999999999998</v>
+      </c>
+      <c r="H23" s="136">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="I23" s="164">
+        <v>0.57143999999999995</v>
+      </c>
+      <c r="J23" s="165">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="K23" s="164">
+        <v>0.65802000000000005</v>
+      </c>
+      <c r="L23" s="165">
+        <v>1.83E-2</v>
+      </c>
+      <c r="M23" s="159">
+        <v>0.67579999999999996</v>
+      </c>
+      <c r="N23" s="160">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="O23" s="164">
+        <v>0.58628000000000002</v>
+      </c>
+      <c r="P23" s="165">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="Q23" s="164">
+        <v>0.61882000000000004</v>
+      </c>
+      <c r="R23" s="165">
+        <v>2.7199999999999998E-2</v>
+      </c>
+      <c r="S23" s="168">
+        <v>0.62990000000000002</v>
+      </c>
+      <c r="T23" s="166">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="U23" s="167">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="V23" s="160">
+        <v>2.52E-2</v>
+      </c>
+      <c r="W23" s="159">
+        <f t="shared" si="0"/>
+        <v>0.30925058823529411</v>
+      </c>
+      <c r="X23" s="160">
+        <f t="shared" si="0"/>
+        <v>0.30196823529411759</v>
+      </c>
+      <c r="Y23" s="102">
+        <f t="shared" si="1"/>
+        <v>0.29952072510080552</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B24" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="161">
+        <f t="shared" ref="C24:V24" si="2">AVERAGE(C2:C23)</f>
+        <v>0.28838181818181818</v>
+      </c>
+      <c r="D24" s="156">
+        <f>AVERAGE(D2:D23)</f>
+        <v>0.11708636363636367</v>
+      </c>
+      <c r="E24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.69495454545454538</v>
+      </c>
+      <c r="F24" s="156">
+        <f t="shared" si="2"/>
+        <v>2.3418181818181817E-2</v>
+      </c>
+      <c r="G24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.6685545454545454</v>
+      </c>
+      <c r="H24" s="172">
+        <f t="shared" si="2"/>
+        <v>2.4604545454545455E-2</v>
+      </c>
+      <c r="I24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.69791727272727266</v>
+      </c>
+      <c r="J24" s="156">
+        <f>AVERAGE(J2:J23)</f>
+        <v>2.8899999999999995E-2</v>
+      </c>
+      <c r="K24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.74456545454545453</v>
+      </c>
+      <c r="L24" s="156">
+        <f>AVERAGE(L2:L23)</f>
+        <v>2.7190909090909089E-2</v>
+      </c>
+      <c r="M24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.75770909090909089</v>
+      </c>
+      <c r="N24" s="156">
+        <f>AVERAGE(N2:N23)</f>
+        <v>1.5713636363636364E-2</v>
+      </c>
+      <c r="O24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.7111054545454546</v>
+      </c>
+      <c r="P24" s="156">
+        <f>AVERAGE(P2:P23)</f>
+        <v>1.9763636363636365E-2</v>
+      </c>
+      <c r="Q24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.73433363636363636</v>
+      </c>
+      <c r="R24" s="156">
+        <f>AVERAGE(R2:R23)</f>
+        <v>2.4190909090909093E-2</v>
+      </c>
+      <c r="S24" s="161">
+        <f t="shared" si="2"/>
+        <v>0.7450681818181818</v>
+      </c>
+      <c r="T24" s="156">
+        <f t="shared" si="2"/>
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="U24" s="169">
+        <f t="shared" si="2"/>
+        <v>0.77444090909090935</v>
+      </c>
+      <c r="V24" s="156">
+        <f t="shared" si="2"/>
+        <v>2.0154545454545456E-2</v>
+      </c>
+      <c r="W24" s="170">
+        <f>AVERAGE(W2:W23)</f>
+        <v>0.37196812834224602</v>
+      </c>
+      <c r="X24" s="157">
+        <f>AVERAGE(X2:X23)</f>
+        <v>0.35630449197860964</v>
+      </c>
+      <c r="Y24" s="102"/>
+      <c r="AK24" s="5">
+        <f>AVERAGE(AK2:AK23)</f>
+        <v>0.73649411764705885</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="K25" s="116"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B29" s="62" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="163" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="155"/>
+      <c r="E29" s="163" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="155"/>
+      <c r="G29" s="163" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="155"/>
+      <c r="I29" s="163" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="155"/>
+      <c r="K29"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="159">
+        <v>0.72489999999999999</v>
+      </c>
+      <c r="D30" s="160">
+        <v>2.4899999999999999E-2</v>
+      </c>
+      <c r="E30" s="167">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="F30" s="160">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="G30" s="159">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="H30" s="160">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="I30" s="159">
+        <f>AVERAGE(C30:G30)</f>
+        <v>0.30869999999999997</v>
+      </c>
+      <c r="J30" s="160">
+        <f>AVERAGE(D30:H30)</f>
+        <v>0.16484000000000004</v>
+      </c>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="159">
+        <v>0.51060000000000005</v>
+      </c>
+      <c r="D31" s="160">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="E31" s="167">
+        <v>0.58169999999999999</v>
+      </c>
+      <c r="F31" s="160">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="G31" s="159">
+        <v>0.54530000000000001</v>
+      </c>
+      <c r="H31" s="160">
+        <v>1.38E-2</v>
+      </c>
+      <c r="I31" s="159">
+        <f>AVERAGE(C31:C31)</f>
+        <v>0.51060000000000005</v>
+      </c>
+      <c r="J31" s="160">
+        <f>AVERAGE(D31:H31)</f>
+        <v>0.24609999999999999</v>
+      </c>
+      <c r="K31"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
+      <c r="B32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="159">
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="D32" s="160">
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="E32" s="167">
+        <v>0.5806</v>
+      </c>
+      <c r="F32" s="160">
+        <v>9.1300000000000006E-2</v>
+      </c>
+      <c r="G32" s="159">
+        <v>0.40579999999999999</v>
+      </c>
+      <c r="H32" s="160">
+        <v>0.25990000000000002</v>
+      </c>
+      <c r="I32" s="159">
+        <f>AVERAGE(C32:C32)</f>
+        <v>0.55910000000000004</v>
+      </c>
+      <c r="J32" s="160">
+        <f>AVERAGE(D32:H32)</f>
+        <v>0.27802000000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B33" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="159">
+        <v>0.69740000000000002</v>
+      </c>
+      <c r="D33" s="160">
+        <v>1.21E-2</v>
+      </c>
+      <c r="E33" s="159">
+        <v>0.57050000000000001</v>
+      </c>
+      <c r="F33" s="160">
+        <v>0.1106</v>
+      </c>
+      <c r="G33" s="167">
+        <v>0.73209999999999997</v>
+      </c>
+      <c r="H33" s="160">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="I33" s="159">
+        <f>AVERAGE(C33:C33)</f>
+        <v>0.69740000000000002</v>
+      </c>
+      <c r="J33" s="160">
+        <f>AVERAGE(D33:H33)</f>
+        <v>0.29158000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="159">
+        <v>0.52429999999999999</v>
+      </c>
+      <c r="D34" s="160">
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="E34" s="167">
+        <v>0.55840000000000001</v>
+      </c>
+      <c r="F34" s="160">
+        <v>0.1009</v>
+      </c>
+      <c r="G34" s="159">
+        <v>0.35070000000000001</v>
+      </c>
+      <c r="H34" s="160">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="I34" s="159">
+        <f>AVERAGE(C34:C34)</f>
+        <v>0.52429999999999999</v>
+      </c>
+      <c r="J34" s="160">
+        <f>AVERAGE(D34:H34)</f>
+        <v>0.27535999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="159">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="D35" s="160">
+        <v>8.5699999999999998E-2</v>
+      </c>
+      <c r="E35" s="167">
+        <v>0.53580000000000005</v>
+      </c>
+      <c r="F35" s="160">
+        <v>0.1108</v>
+      </c>
+      <c r="G35" s="159">
+        <v>0.33660000000000001</v>
+      </c>
+      <c r="H35" s="160">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="I35" s="159">
+        <f>AVERAGE(C35:C35)</f>
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="J35" s="160">
+        <f>AVERAGE(D35:H35)</f>
+        <v>0.27898000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="159">
+        <v>0.52070000000000005</v>
+      </c>
+      <c r="D36" s="160">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="E36" s="167">
+        <v>0.52959999999999996</v>
+      </c>
+      <c r="F36" s="160">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="G36" s="159">
+        <v>0.50629999999999997</v>
+      </c>
+      <c r="H36" s="160">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="I36" s="159">
+        <f>AVERAGE(C36:C36)</f>
+        <v>0.52070000000000005</v>
+      </c>
+      <c r="J36" s="160">
+        <f>AVERAGE(D36:H36)</f>
+        <v>0.23796</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="159">
+        <v>0.4289</v>
+      </c>
+      <c r="D37" s="160">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="E37" s="159">
+        <v>0.4874</v>
+      </c>
+      <c r="F37" s="160">
+        <v>8.9800000000000005E-2</v>
+      </c>
+      <c r="G37" s="167">
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="H37" s="160">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="I37" s="159">
+        <f>AVERAGE(C37:C37)</f>
+        <v>0.4289</v>
+      </c>
+      <c r="J37" s="160">
+        <f>AVERAGE(D37:H37)</f>
+        <v>0.24922</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="159">
+        <v>0.57030000000000003</v>
+      </c>
+      <c r="D38" s="160">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="E38" s="159">
+        <v>0.49030000000000001</v>
+      </c>
+      <c r="F38" s="160">
+        <v>0.18099999999999999</v>
+      </c>
+      <c r="G38" s="167">
+        <v>0.57969999999999999</v>
+      </c>
+      <c r="H38" s="160">
+        <v>0.25750000000000001</v>
+      </c>
+      <c r="I38" s="159">
+        <f>AVERAGE(C38:C38)</f>
+        <v>0.57030000000000003</v>
+      </c>
+      <c r="J38" s="160">
+        <f>AVERAGE(D38:H38)</f>
+        <v>0.30818000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="159">
+        <v>0.5161</v>
+      </c>
+      <c r="D39" s="160">
+        <v>2.58E-2</v>
+      </c>
+      <c r="E39" s="159">
+        <v>0.50019999999999998</v>
+      </c>
+      <c r="F39" s="160">
+        <v>2.6200000000000001E-2</v>
+      </c>
+      <c r="G39" s="167">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="H39" s="160">
+        <v>8.2699999999999996E-2</v>
+      </c>
+      <c r="I39" s="159">
+        <f>AVERAGE(C39:C39)</f>
+        <v>0.5161</v>
+      </c>
+      <c r="J39" s="160">
+        <f>AVERAGE(D39:H39)</f>
+        <v>0.24177999999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="167">
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="D40" s="160">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="E40" s="159">
+        <v>0.4783</v>
+      </c>
+      <c r="F40" s="160">
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="G40" s="159">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="H40" s="160">
+        <v>0.2213</v>
+      </c>
+      <c r="I40" s="159">
+        <f>AVERAGE(C40:C40)</f>
+        <v>0.51080000000000003</v>
+      </c>
+      <c r="J40" s="160">
+        <f>AVERAGE(D40:H40)</f>
+        <v>0.25166000000000005</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="167">
+        <v>0.5776</v>
+      </c>
+      <c r="D41" s="160">
+        <v>5.4699999999999999E-2</v>
+      </c>
+      <c r="E41" s="159">
+        <v>0.46400000000000002</v>
+      </c>
+      <c r="F41" s="160">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="G41" s="159">
+        <v>0.22409999999999999</v>
+      </c>
+      <c r="H41" s="160">
+        <v>0.2437</v>
+      </c>
+      <c r="I41" s="159">
+        <f>AVERAGE(C41:C41)</f>
+        <v>0.5776</v>
+      </c>
+      <c r="J41" s="160">
+        <f>AVERAGE(D41:H41)</f>
+        <v>0.2379</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="159">
+        <v>0.52769999999999995</v>
+      </c>
+      <c r="D42" s="160">
+        <v>9.6600000000000005E-2</v>
+      </c>
+      <c r="E42" s="159">
+        <v>0.52280000000000004</v>
+      </c>
+      <c r="F42" s="160">
+        <v>4.4900000000000002E-2</v>
+      </c>
+      <c r="G42" s="167">
+        <v>0.55059999999999998</v>
+      </c>
+      <c r="H42" s="160">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="I42" s="159">
+        <f>AVERAGE(C42:C42)</f>
+        <v>0.52769999999999995</v>
+      </c>
+      <c r="J42" s="160">
+        <f>AVERAGE(D42:H42)</f>
+        <v>0.29608000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="159">
+        <v>0.42649999999999999</v>
+      </c>
+      <c r="D43" s="160">
+        <v>0.18690000000000001</v>
+      </c>
+      <c r="E43" s="159">
+        <v>0.4677</v>
+      </c>
+      <c r="F43" s="160">
+        <v>0.1825</v>
+      </c>
+      <c r="G43" s="167">
+        <v>0.59319999999999995</v>
+      </c>
+      <c r="H43" s="160">
+        <v>2.5899999999999999E-2</v>
+      </c>
+      <c r="I43" s="159">
+        <f>AVERAGE(C43:C43)</f>
+        <v>0.42649999999999999</v>
+      </c>
+      <c r="J43" s="160">
+        <f>AVERAGE(D43:H43)</f>
+        <v>0.29124</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="159">
+        <v>0.45319999999999999</v>
+      </c>
+      <c r="D44" s="160">
+        <v>2.4E-2</v>
+      </c>
+      <c r="E44" s="159">
+        <v>0.33019999999999999</v>
+      </c>
+      <c r="F44" s="160">
+        <v>0.1075</v>
+      </c>
+      <c r="G44" s="167">
+        <v>0.46529999999999999</v>
+      </c>
+      <c r="H44" s="160">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="I44" s="159">
+        <f>AVERAGE(C44:C44)</f>
+        <v>0.45319999999999999</v>
+      </c>
+      <c r="J44" s="160">
+        <f>AVERAGE(D44:H44)</f>
+        <v>0.19070000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B45" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="167">
+        <v>0.60660000000000003</v>
+      </c>
+      <c r="D45" s="160">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="E45" s="159">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="F45" s="160">
+        <v>0.2021</v>
+      </c>
+      <c r="G45" s="159">
+        <v>0.43569999999999998</v>
+      </c>
+      <c r="H45" s="160">
+        <v>0.32850000000000001</v>
+      </c>
+      <c r="I45" s="159">
+        <f>AVERAGE(C45:C45)</f>
+        <v>0.60660000000000003</v>
+      </c>
+      <c r="J45" s="160">
+        <f>AVERAGE(D45:H45)</f>
+        <v>0.30034</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="167">
+        <v>0.50190000000000001</v>
+      </c>
+      <c r="D46" s="160">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="E46" s="159">
+        <v>0.49940000000000001</v>
+      </c>
+      <c r="F46" s="160">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="G46" s="159">
+        <v>0.33079999999999998</v>
+      </c>
+      <c r="H46" s="160">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="I46" s="159">
+        <f>AVERAGE(C46:C46)</f>
+        <v>0.50190000000000001</v>
+      </c>
+      <c r="J46" s="160">
+        <f>AVERAGE(D46:H46)</f>
+        <v>0.22364000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="159">
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="D47" s="160">
+        <v>6.1699999999999998E-2</v>
+      </c>
+      <c r="E47" s="159">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="F47" s="160">
+        <v>0.10489999999999999</v>
+      </c>
+      <c r="G47" s="167">
+        <v>0.46779999999999999</v>
+      </c>
+      <c r="H47" s="160">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="I47" s="159">
+        <f>AVERAGE(C47:C47)</f>
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="J47" s="160">
+        <f>AVERAGE(D47:H47)</f>
+        <v>0.18745999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="167">
+        <v>0.3488</v>
+      </c>
+      <c r="D48" s="160">
+        <v>0.1077</v>
+      </c>
+      <c r="E48" s="159">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="F48" s="160">
+        <v>0.1386</v>
+      </c>
+      <c r="G48" s="159">
+        <v>0.3392</v>
+      </c>
+      <c r="H48" s="160">
+        <v>0.17749999999999999</v>
+      </c>
+      <c r="I48" s="159">
+        <f>AVERAGE(C48:C48)</f>
+        <v>0.3488</v>
+      </c>
+      <c r="J48" s="160">
+        <f>AVERAGE(D48:H48)</f>
+        <v>0.2172</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="159">
+        <v>0.50570000000000004</v>
+      </c>
+      <c r="D49" s="160">
+        <v>7.22E-2</v>
+      </c>
+      <c r="E49" s="167">
+        <v>0.53680000000000005</v>
+      </c>
+      <c r="F49" s="160">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="G49" s="159">
+        <v>0.40229999999999999</v>
+      </c>
+      <c r="H49" s="116">
+        <v>0.22259999999999999</v>
+      </c>
+      <c r="I49" s="159">
+        <f>AVERAGE(C49:C49)</f>
+        <v>0.50570000000000004</v>
+      </c>
+      <c r="J49" s="160">
+        <f>AVERAGE(D49:H49)</f>
+        <v>0.25857999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B50" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="159">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="D50" s="160">
+        <v>0.22520000000000001</v>
+      </c>
+      <c r="E50" s="159">
+        <v>0.48930000000000001</v>
+      </c>
+      <c r="F50" s="160">
+        <v>7.7899999999999997E-2</v>
+      </c>
+      <c r="G50" s="167">
+        <v>0.58209999999999995</v>
+      </c>
+      <c r="H50" s="160">
+        <v>0.22969999999999999</v>
+      </c>
+      <c r="I50" s="159">
+        <f>AVERAGE(C50:C50)</f>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="J50" s="160">
+        <f>AVERAGE(D50:H50)</f>
+        <v>0.32083999999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="167">
+        <v>0.31169999999999998</v>
+      </c>
+      <c r="D51" s="160">
+        <v>8.4699999999999998E-2</v>
+      </c>
+      <c r="E51" s="159">
+        <v>0.27089999999999997</v>
+      </c>
+      <c r="F51" s="160">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="G51" s="159">
+        <v>0.25569999999999998</v>
+      </c>
+      <c r="H51" s="160">
+        <v>0.1173</v>
+      </c>
+      <c r="I51" s="159">
+        <f>AVERAGE(C51:C51)</f>
+        <v>0.31169999999999998</v>
+      </c>
+      <c r="J51" s="160">
+        <f>AVERAGE(D51:H51)</f>
+        <v>0.1497</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B52" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" s="173">
+        <f>AVERAGE(C30:C51)</f>
+        <v>0.51188636363636375</v>
+      </c>
+      <c r="D52" s="157">
+        <f>AVERAGE(D30:D51)</f>
+        <v>7.1004545454545459E-2</v>
+      </c>
+      <c r="E52" s="170">
+        <f>AVERAGE(E30:E51)</f>
+        <v>0.4877227272727272</v>
+      </c>
+      <c r="F52" s="157">
+        <f>AVERAGE(F30:F51)</f>
+        <v>9.3149999999999983E-2</v>
+      </c>
+      <c r="G52" s="170">
+        <f>AVERAGE(G30:G51)</f>
+        <v>0.44055454545454542</v>
+      </c>
+      <c r="H52" s="157">
+        <f>AVERAGE(H30:H51)</f>
+        <v>0.15696818181818181</v>
+      </c>
+      <c r="I52" s="170">
+        <f>AVERAGE(I30:I51)</f>
+        <v>0.49296818181818192</v>
+      </c>
+      <c r="J52" s="157">
+        <f>AVERAGE(J30:J51)</f>
+        <v>0.24987999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="H56" s="154"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3699033A-619E-42E5-83A7-5668B557271C}">
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5560,7 +8453,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F42386-BE8F-46D2-A796-8CB49AA40B36}">
   <dimension ref="A1:S53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5579,54 +8472,54 @@
       <c r="B1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
       <c r="F1" s="142"/>
-      <c r="G1" s="141" t="s">
+      <c r="G1" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
       <c r="J1" s="142"/>
-      <c r="K1" s="140" t="s">
+      <c r="K1" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
       <c r="B2" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="141" t="s">
+      <c r="C2" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="140"/>
-      <c r="E2" s="140" t="s">
+      <c r="D2" s="141"/>
+      <c r="E2" s="141" t="s">
         <v>59</v>
       </c>
       <c r="F2" s="142"/>
-      <c r="G2" s="141" t="s">
+      <c r="G2" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140" t="s">
+      <c r="H2" s="141"/>
+      <c r="I2" s="141" t="s">
         <v>59</v>
       </c>
       <c r="J2" s="142"/>
-      <c r="K2" s="140" t="s">
+      <c r="K2" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140" t="s">
+      <c r="L2" s="141"/>
+      <c r="M2" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="140"/>
+      <c r="N2" s="141"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
@@ -6699,24 +9592,24 @@
       <c r="B28" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="141" t="s">
+      <c r="C28" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
       <c r="F28" s="142"/>
-      <c r="G28" s="141" t="s">
+      <c r="G28" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="H28" s="140"/>
-      <c r="I28" s="140"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
       <c r="J28" s="142"/>
-      <c r="K28" s="140" t="s">
+      <c r="K28" s="141" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="140"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="140"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
+      <c r="N28" s="141"/>
       <c r="P28" s="68"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
@@ -6724,30 +9617,30 @@
       <c r="B29" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="141" t="s">
+      <c r="C29" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="140"/>
-      <c r="E29" s="140" t="s">
+      <c r="D29" s="141"/>
+      <c r="E29" s="141" t="s">
         <v>59</v>
       </c>
       <c r="F29" s="142"/>
-      <c r="G29" s="141" t="s">
+      <c r="G29" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="140"/>
-      <c r="I29" s="140" t="s">
+      <c r="H29" s="141"/>
+      <c r="I29" s="141" t="s">
         <v>59</v>
       </c>
       <c r="J29" s="142"/>
-      <c r="K29" s="140" t="s">
+      <c r="K29" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="140"/>
-      <c r="M29" s="140" t="s">
+      <c r="L29" s="141"/>
+      <c r="M29" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="N29" s="140"/>
+      <c r="N29" s="141"/>
       <c r="P29" s="68"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
@@ -8108,6 +11001,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="K28:N28"/>
@@ -8117,22 +11019,13 @@
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
     <mergeCell ref="M29:N29"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29EADB14-493D-4AA6-B1C8-5DB3EEA4FD6E}">
   <dimension ref="A1:O134"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8152,43 +11045,43 @@
       <c r="B1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="49"/>
       <c r="B2" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="146" t="s">
+      <c r="C2" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="146" t="s">
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="150"/>
-      <c r="K2" s="146" t="s">
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="145"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
@@ -8197,30 +11090,30 @@
       <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="145" t="s">
+      <c r="D3" s="150"/>
+      <c r="E3" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="149"/>
-      <c r="G3" s="143" t="s">
+      <c r="F3" s="151"/>
+      <c r="G3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="145" t="s">
+      <c r="H3" s="150"/>
+      <c r="I3" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="149"/>
-      <c r="K3" s="143" t="s">
+      <c r="J3" s="151"/>
+      <c r="K3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="144"/>
-      <c r="M3" s="148" t="s">
+      <c r="L3" s="150"/>
+      <c r="M3" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="148"/>
+      <c r="N3" s="143"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
@@ -9248,71 +12141,71 @@
       <c r="B28" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="145" t="s">
+      <c r="C28" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="140"/>
-      <c r="M28" s="140"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
+      <c r="K28" s="141"/>
+      <c r="L28" s="141"/>
+      <c r="M28" s="141"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B29" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="150"/>
-      <c r="G29" s="146" t="s">
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="150"/>
-      <c r="K29" s="146" t="s">
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="146"/>
+      <c r="K29" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="L29" s="147"/>
-      <c r="M29" s="147"/>
-      <c r="N29" s="147"/>
+      <c r="L29" s="145"/>
+      <c r="M29" s="145"/>
+      <c r="N29" s="145"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B30" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="143" t="s">
+      <c r="C30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="144"/>
-      <c r="E30" s="145" t="s">
+      <c r="D30" s="150"/>
+      <c r="E30" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="149"/>
-      <c r="G30" s="143" t="s">
+      <c r="F30" s="151"/>
+      <c r="G30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="144"/>
-      <c r="I30" s="145" t="s">
+      <c r="H30" s="150"/>
+      <c r="I30" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="149"/>
-      <c r="K30" s="143" t="s">
+      <c r="J30" s="151"/>
+      <c r="K30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="L30" s="144"/>
-      <c r="M30" s="148" t="s">
+      <c r="L30" s="150"/>
+      <c r="M30" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="N30" s="148"/>
+      <c r="N30" s="143"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B31" s="22" t="s">
@@ -10274,71 +13167,71 @@
       <c r="B55" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C55" s="151" t="s">
+      <c r="C55" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="145"/>
-      <c r="E55" s="145"/>
-      <c r="F55" s="145"/>
-      <c r="G55" s="145"/>
-      <c r="H55" s="145"/>
-      <c r="I55" s="145"/>
-      <c r="J55" s="145"/>
-      <c r="K55" s="145"/>
-      <c r="L55" s="145"/>
-      <c r="M55" s="145"/>
+      <c r="D55" s="147"/>
+      <c r="E55" s="147"/>
+      <c r="F55" s="147"/>
+      <c r="G55" s="147"/>
+      <c r="H55" s="147"/>
+      <c r="I55" s="147"/>
+      <c r="J55" s="147"/>
+      <c r="K55" s="147"/>
+      <c r="L55" s="147"/>
+      <c r="M55" s="147"/>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="146" t="s">
+      <c r="C56" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="D56" s="147"/>
-      <c r="E56" s="147"/>
-      <c r="F56" s="150"/>
-      <c r="G56" s="146" t="s">
+      <c r="D56" s="145"/>
+      <c r="E56" s="145"/>
+      <c r="F56" s="146"/>
+      <c r="G56" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="H56" s="147"/>
-      <c r="I56" s="147"/>
-      <c r="J56" s="150"/>
-      <c r="K56" s="146" t="s">
+      <c r="H56" s="145"/>
+      <c r="I56" s="145"/>
+      <c r="J56" s="146"/>
+      <c r="K56" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="L56" s="147"/>
-      <c r="M56" s="147"/>
-      <c r="N56" s="147"/>
+      <c r="L56" s="145"/>
+      <c r="M56" s="145"/>
+      <c r="N56" s="145"/>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C57" s="143" t="s">
+      <c r="C57" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D57" s="144"/>
-      <c r="E57" s="145" t="s">
+      <c r="D57" s="150"/>
+      <c r="E57" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="F57" s="149"/>
+      <c r="F57" s="151"/>
       <c r="G57" s="17" t="s">
         <v>52</v>
       </c>
       <c r="H57" s="19"/>
-      <c r="I57" s="145" t="s">
+      <c r="I57" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="J57" s="149"/>
-      <c r="K57" s="143" t="s">
+      <c r="J57" s="151"/>
+      <c r="K57" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="L57" s="144"/>
-      <c r="M57" s="148" t="s">
+      <c r="L57" s="150"/>
+      <c r="M57" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="N57" s="148"/>
+      <c r="N57" s="143"/>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" s="22" t="s">
@@ -11299,71 +14192,71 @@
       <c r="B82" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C82" s="145" t="s">
+      <c r="C82" s="147" t="s">
         <v>55</v>
       </c>
-      <c r="D82" s="145"/>
-      <c r="E82" s="145"/>
-      <c r="F82" s="145"/>
-      <c r="G82" s="145"/>
-      <c r="H82" s="145"/>
-      <c r="I82" s="145"/>
-      <c r="J82" s="145"/>
-      <c r="K82" s="140"/>
-      <c r="L82" s="140"/>
-      <c r="M82" s="140"/>
+      <c r="D82" s="147"/>
+      <c r="E82" s="147"/>
+      <c r="F82" s="147"/>
+      <c r="G82" s="147"/>
+      <c r="H82" s="147"/>
+      <c r="I82" s="147"/>
+      <c r="J82" s="147"/>
+      <c r="K82" s="141"/>
+      <c r="L82" s="141"/>
+      <c r="M82" s="141"/>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B83" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C83" s="146" t="s">
+      <c r="C83" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="147"/>
-      <c r="E83" s="147"/>
-      <c r="F83" s="147"/>
-      <c r="G83" s="146" t="s">
+      <c r="D83" s="145"/>
+      <c r="E83" s="145"/>
+      <c r="F83" s="145"/>
+      <c r="G83" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="H83" s="147"/>
-      <c r="I83" s="147"/>
-      <c r="J83" s="150"/>
-      <c r="K83" s="146" t="s">
+      <c r="H83" s="145"/>
+      <c r="I83" s="145"/>
+      <c r="J83" s="146"/>
+      <c r="K83" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="L83" s="147"/>
-      <c r="M83" s="147"/>
-      <c r="N83" s="147"/>
+      <c r="L83" s="145"/>
+      <c r="M83" s="145"/>
+      <c r="N83" s="145"/>
     </row>
     <row r="84" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B84" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C84" s="143" t="s">
+      <c r="C84" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D84" s="144"/>
-      <c r="E84" s="145" t="s">
+      <c r="D84" s="150"/>
+      <c r="E84" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="F84" s="149"/>
-      <c r="G84" s="143" t="s">
+      <c r="F84" s="151"/>
+      <c r="G84" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H84" s="144"/>
-      <c r="I84" s="145" t="s">
+      <c r="H84" s="150"/>
+      <c r="I84" s="147" t="s">
         <v>53</v>
       </c>
       <c r="J84" s="142"/>
-      <c r="K84" s="143" t="s">
+      <c r="K84" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="L84" s="144"/>
-      <c r="M84" s="148" t="s">
+      <c r="L84" s="150"/>
+      <c r="M84" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="N84" s="148"/>
+      <c r="N84" s="143"/>
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B85" s="22" t="s">
@@ -12324,71 +15217,71 @@
       <c r="B109" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C109" s="145" t="s">
+      <c r="C109" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="D109" s="145"/>
-      <c r="E109" s="145"/>
-      <c r="F109" s="145"/>
-      <c r="G109" s="145"/>
-      <c r="H109" s="145"/>
-      <c r="I109" s="145"/>
-      <c r="J109" s="145"/>
-      <c r="K109" s="140"/>
-      <c r="L109" s="140"/>
-      <c r="M109" s="140"/>
+      <c r="D109" s="147"/>
+      <c r="E109" s="147"/>
+      <c r="F109" s="147"/>
+      <c r="G109" s="147"/>
+      <c r="H109" s="147"/>
+      <c r="I109" s="147"/>
+      <c r="J109" s="147"/>
+      <c r="K109" s="141"/>
+      <c r="L109" s="141"/>
+      <c r="M109" s="141"/>
     </row>
     <row r="110" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B110" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C110" s="146" t="s">
+      <c r="C110" s="144" t="s">
         <v>61</v>
       </c>
-      <c r="D110" s="147"/>
-      <c r="E110" s="147"/>
-      <c r="F110" s="147"/>
-      <c r="G110" s="146" t="s">
+      <c r="D110" s="145"/>
+      <c r="E110" s="145"/>
+      <c r="F110" s="145"/>
+      <c r="G110" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="H110" s="147"/>
-      <c r="I110" s="147"/>
-      <c r="J110" s="150"/>
-      <c r="K110" s="146" t="s">
+      <c r="H110" s="145"/>
+      <c r="I110" s="145"/>
+      <c r="J110" s="146"/>
+      <c r="K110" s="144" t="s">
         <v>59</v>
       </c>
-      <c r="L110" s="147"/>
-      <c r="M110" s="147"/>
-      <c r="N110" s="147"/>
+      <c r="L110" s="145"/>
+      <c r="M110" s="145"/>
+      <c r="N110" s="145"/>
     </row>
     <row r="111" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B111" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C111" s="143" t="s">
+      <c r="C111" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D111" s="144"/>
-      <c r="E111" s="145" t="s">
+      <c r="D111" s="150"/>
+      <c r="E111" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="F111" s="149"/>
-      <c r="G111" s="143" t="s">
+      <c r="F111" s="151"/>
+      <c r="G111" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H111" s="144"/>
-      <c r="I111" s="140" t="s">
+      <c r="H111" s="150"/>
+      <c r="I111" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="J111" s="149"/>
-      <c r="K111" s="143" t="s">
+      <c r="J111" s="151"/>
+      <c r="K111" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="L111" s="144"/>
-      <c r="M111" s="148" t="s">
+      <c r="L111" s="150"/>
+      <c r="M111" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="N111" s="148"/>
+      <c r="N111" s="143"/>
     </row>
     <row r="112" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B112" s="22" t="s">
@@ -13347,6 +16240,39 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="G111:H111"/>
+    <mergeCell ref="C82:M82"/>
+    <mergeCell ref="K110:N110"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="G56:J56"/>
+    <mergeCell ref="K56:N56"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I111:J111"/>
+    <mergeCell ref="G110:J110"/>
+    <mergeCell ref="C109:M109"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="C83:F83"/>
     <mergeCell ref="M30:N30"/>
     <mergeCell ref="G83:J83"/>
     <mergeCell ref="K83:N83"/>
@@ -13363,46 +16289,13 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I111:J111"/>
-    <mergeCell ref="G110:J110"/>
-    <mergeCell ref="C109:M109"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="K84:L84"/>
-    <mergeCell ref="M84:N84"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="C83:F83"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="G56:J56"/>
-    <mergeCell ref="K56:N56"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="G111:H111"/>
-    <mergeCell ref="C82:M82"/>
-    <mergeCell ref="K110:N110"/>
-    <mergeCell ref="K111:L111"/>
-    <mergeCell ref="M111:N111"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="C110:F110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="E111:F111"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B2204D-B125-4EB2-8006-68788CE54501}">
   <dimension ref="B1:M53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13414,16 +16307,16 @@
       <c r="B1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
       <c r="K1" s="130"/>
       <c r="L1" s="130"/>
       <c r="M1" s="130"/>
@@ -13432,39 +16325,39 @@
       <c r="B2" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="146" t="s">
+      <c r="C2" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="146" t="s">
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="140" t="s">
+      <c r="D3" s="150"/>
+      <c r="E3" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="149"/>
-      <c r="G3" s="143" t="s">
+      <c r="F3" s="151"/>
+      <c r="G3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="148" t="s">
+      <c r="H3" s="150"/>
+      <c r="I3" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="148"/>
+      <c r="J3" s="143"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="22" t="s">
@@ -14145,54 +17038,54 @@
       <c r="B28" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="145" t="s">
+      <c r="C28" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="144" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="150"/>
-      <c r="G29" s="146" t="s">
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="144" t="s">
         <v>77</v>
       </c>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="147"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="143" t="s">
+      <c r="C30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="144"/>
-      <c r="E30" s="140" t="s">
+      <c r="D30" s="150"/>
+      <c r="E30" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="149"/>
-      <c r="G30" s="143" t="s">
+      <c r="F30" s="151"/>
+      <c r="G30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="144"/>
-      <c r="I30" s="148" t="s">
+      <c r="H30" s="150"/>
+      <c r="I30" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="148"/>
+      <c r="J30" s="143"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="22" t="s">
@@ -14871,6 +17764,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="C1:J1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:J2"/>
@@ -14878,19 +17778,12 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0005D249-6C7C-42A8-A69E-C1EA58715686}">
   <dimension ref="B1:M53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14902,16 +17795,16 @@
       <c r="B1" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="145"/>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
       <c r="K1" s="130"/>
       <c r="L1" s="130"/>
       <c r="M1" s="130"/>
@@ -14920,39 +17813,39 @@
       <c r="B2" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="146" t="s">
+      <c r="C2" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="146" t="s">
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="144" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="144"/>
-      <c r="E3" s="140" t="s">
+      <c r="D3" s="150"/>
+      <c r="E3" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="149"/>
-      <c r="G3" s="143" t="s">
+      <c r="F3" s="151"/>
+      <c r="G3" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="144"/>
-      <c r="I3" s="148" t="s">
+      <c r="H3" s="150"/>
+      <c r="I3" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="148"/>
+      <c r="J3" s="143"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="22" t="s">
@@ -15633,54 +18526,54 @@
       <c r="B28" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="145" t="s">
+      <c r="C28" s="147" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="147"/>
+      <c r="F28" s="147"/>
+      <c r="G28" s="147"/>
+      <c r="H28" s="147"/>
+      <c r="I28" s="147"/>
+      <c r="J28" s="147"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="144" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="147"/>
-      <c r="E29" s="147"/>
-      <c r="F29" s="150"/>
-      <c r="G29" s="146" t="s">
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="144" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="147"/>
-      <c r="I29" s="147"/>
-      <c r="J29" s="147"/>
+      <c r="H29" s="145"/>
+      <c r="I29" s="145"/>
+      <c r="J29" s="145"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="143" t="s">
+      <c r="C30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="144"/>
-      <c r="E30" s="140" t="s">
+      <c r="D30" s="150"/>
+      <c r="E30" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="149"/>
-      <c r="G30" s="143" t="s">
+      <c r="F30" s="151"/>
+      <c r="G30" s="149" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="144"/>
-      <c r="I30" s="148" t="s">
+      <c r="H30" s="150"/>
+      <c r="I30" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="148"/>
+      <c r="J30" s="143"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="22" t="s">
@@ -16007,6 +18900,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C28:J28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:J30"/>
     <mergeCell ref="C1:J1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:J2"/>
@@ -16014,13 +18914,6 @@
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="I3:J3"/>
-    <mergeCell ref="C28:J28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
